--- a/order_forms/039_personal_chef_booking_form--order_forms.xlsx
+++ b/order_forms/039_personal_chef_booking_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>party_planning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Party Planning</t>
         </is>
       </c>
     </row>
@@ -1199,29 +1199,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>party_planning</t>
+          <t>private_dining</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Party Planning</t>
+          <t>Private Dining</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>chef_service_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>private_dining</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Private Dining</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1233,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>private</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>form_status_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Sent</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sent</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_status_choices</t>
+          <t>submitted_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1386,27 +1386,10 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>submitted_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
